--- a/output/Chp2_tables/Chapter 2 - Table 2.xlsx
+++ b/output/Chp2_tables/Chapter 2 - Table 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
   <si>
     <t>Total Number of PLHIV in PNG 2025</t>
   </si>
@@ -46,406 +46,403 @@
     <t>Newly VF due to Drug Resistance 2030</t>
   </si>
   <si>
-    <t>81,377 (71,017-94,183)</t>
-  </si>
-  <si>
-    <t>81,241 (70,895-93,959)</t>
-  </si>
-  <si>
-    <t>81,121 (70,806-93,704)</t>
-  </si>
-  <si>
-    <t>81,015 (70,738-93,533)</t>
-  </si>
-  <si>
-    <t>81,241 (70,894-93,959)</t>
-  </si>
-  <si>
-    <t>81,122 (70,804-93,698)</t>
-  </si>
-  <si>
-    <t>81,017 (70,736-93,524)</t>
-  </si>
-  <si>
-    <t>81,162 (70,811-93,755)</t>
-  </si>
-  <si>
-    <t>80,993 (70,651-93,427)</t>
-  </si>
-  <si>
-    <t>80,851 (70,510-93,249)</t>
-  </si>
-  <si>
-    <t>81,162 (70,810-93,753)</t>
-  </si>
-  <si>
-    <t>80,995 (70,650-93,427)</t>
-  </si>
-  <si>
-    <t>80,850 (70,510-93,249)</t>
-  </si>
-  <si>
-    <t>81,613 (71,263-94,464)</t>
-  </si>
-  <si>
-    <t>110,336 (86,498-154,194)</t>
-  </si>
-  <si>
-    <t>109,735 (86,121-153,241)</t>
-  </si>
-  <si>
-    <t>109,222 (85,760-152,525)</t>
-  </si>
-  <si>
-    <t>108,833 (85,109-151,975)</t>
-  </si>
-  <si>
-    <t>109,651 (86,119-153,214)</t>
-  </si>
-  <si>
-    <t>109,133 (85,638-152,457)</t>
-  </si>
-  <si>
-    <t>108,708 (84,915-151,860)</t>
-  </si>
-  <si>
-    <t>108,869 (85,540-152,417)</t>
-  </si>
-  <si>
-    <t>107,600 (84,404-151,052)</t>
-  </si>
-  <si>
-    <t>106,551 (83,559-149,836)</t>
-  </si>
-  <si>
-    <t>108,816 (85,527-152,394)</t>
-  </si>
-  <si>
-    <t>107,561 (84,359-151,001)</t>
-  </si>
-  <si>
-    <t>106,438 (83,490-149,739)</t>
-  </si>
-  <si>
-    <t>111,785 (87,217-155,258)</t>
-  </si>
-  <si>
-    <t>7,843 (5,121-12,502)</t>
-  </si>
-  <si>
-    <t>7,751 (5,049-12,450)</t>
-  </si>
-  <si>
-    <t>7,701 (5,015-12,406)</t>
-  </si>
-  <si>
-    <t>7,659 (4,988-12,361)</t>
-  </si>
-  <si>
-    <t>7,749 (5,048-12,450)</t>
-  </si>
-  <si>
-    <t>7,699 (5,014-12,407)</t>
-  </si>
-  <si>
-    <t>7,654 (4,987-12,367)</t>
-  </si>
-  <si>
-    <t>7,669 (5,006-12,408)</t>
-  </si>
-  <si>
-    <t>7,524 (4,902-12,275)</t>
-  </si>
-  <si>
-    <t>7,419 (4,794-12,155)</t>
-  </si>
-  <si>
-    <t>7,668 (5,006-12,408)</t>
-  </si>
-  <si>
-    <t>7,521 (4,900-12,272)</t>
-  </si>
-  <si>
-    <t>7,416 (4,791-12,149)</t>
-  </si>
-  <si>
-    <t>8,005 (5,241-12,787)</t>
-  </si>
-  <si>
-    <t>10,206 (5,767-21,101)</t>
-  </si>
-  <si>
-    <t>10,034 (5,684-20,876)</t>
-  </si>
-  <si>
-    <t>9,917 (5,613-20,719)</t>
-  </si>
-  <si>
-    <t>9,773 (5,557-20,562)</t>
-  </si>
-  <si>
-    <t>9,989 (5,673-20,862)</t>
-  </si>
-  <si>
-    <t>9,804 (5,579-20,643)</t>
-  </si>
-  <si>
-    <t>9,687 (5,470-20,544)</t>
-  </si>
-  <si>
-    <t>9,712 (5,444-20,524)</t>
-  </si>
-  <si>
-    <t>9,310 (5,105-20,183)</t>
-  </si>
-  <si>
-    <t>9,079 (4,934-19,916)</t>
-  </si>
-  <si>
-    <t>9,688 (5,435-20,538)</t>
-  </si>
-  <si>
-    <t>9,281 (5,075-20,181)</t>
-  </si>
-  <si>
-    <t>9,022 (4,833-19,884)</t>
-  </si>
-  <si>
-    <t>10,562 (6,057-21,856)</t>
-  </si>
-  <si>
-    <t>1,962 (735-4,543)</t>
-  </si>
-  <si>
-    <t>1,939 (722-4,509)</t>
-  </si>
-  <si>
-    <t>1,921 (712-4,483)</t>
-  </si>
-  <si>
-    <t>1,907 (705-4,463)</t>
-  </si>
-  <si>
-    <t>1,938 (722-4,509)</t>
-  </si>
-  <si>
-    <t>1,919 (711-4,483)</t>
-  </si>
-  <si>
-    <t>1,903 (703-4,460)</t>
-  </si>
-  <si>
-    <t>1,849 (678-4,407)</t>
-  </si>
-  <si>
-    <t>1,759 (644-4,209)</t>
-  </si>
-  <si>
-    <t>1,679 (612-4,059)</t>
-  </si>
-  <si>
-    <t>1,848 (679-4,406)</t>
-  </si>
-  <si>
-    <t>1,756 (644-4,196)</t>
-  </si>
-  <si>
-    <t>1,674 (612-4,052)</t>
-  </si>
-  <si>
-    <t>2,143 (798-4,767)</t>
-  </si>
-  <si>
-    <t>2,719 (870-7,988)</t>
-  </si>
-  <si>
-    <t>2,645 (841-7,848)</t>
-  </si>
-  <si>
-    <t>2,610 (821-7,745)</t>
-  </si>
-  <si>
-    <t>2,574 (806-7,667)</t>
-  </si>
-  <si>
-    <t>2,632 (837-7,775)</t>
-  </si>
-  <si>
-    <t>2,556 (812-7,629)</t>
-  </si>
-  <si>
-    <t>2,503 (789-7,361)</t>
-  </si>
-  <si>
-    <t>2,353 (716-7,153)</t>
-  </si>
-  <si>
-    <t>2,110 (604-6,638)</t>
-  </si>
-  <si>
-    <t>1,914 (523-6,250)</t>
-  </si>
-  <si>
-    <t>2,340 (713-7,136)</t>
-  </si>
-  <si>
-    <t>2,083 (596-6,361)</t>
-  </si>
-  <si>
-    <t>1,870 (517-5,919)</t>
-  </si>
-  <si>
-    <t>3,188 (1,116-8,469)</t>
-  </si>
-  <si>
-    <t>87.8% (81.1%-92.2%)</t>
-  </si>
-  <si>
-    <t>88.5% (81.9%-92.7%)</t>
-  </si>
-  <si>
-    <t>88.9% (82.3%-93.2%)</t>
-  </si>
-  <si>
-    <t>89.3% (82.7%-93.5%)</t>
-  </si>
-  <si>
-    <t>89.3% (82.9%-93.5%)</t>
-  </si>
-  <si>
-    <t>89.5% (83.6%-93.5%)</t>
-  </si>
-  <si>
-    <t>90.8% (85.4%-94.5%)</t>
-  </si>
-  <si>
-    <t>91.9% (86.8%-95.3%)</t>
-  </si>
-  <si>
-    <t>91.9% (86.9%-95.4%)</t>
-  </si>
-  <si>
-    <t>86.1% (77.8%-91.8%)</t>
-  </si>
-  <si>
-    <t>89.4% (82.5%-93.7%)</t>
-  </si>
-  <si>
-    <t>90.1% (83.5%-94.2%)</t>
-  </si>
-  <si>
-    <t>90.7% (84.0%-94.6%)</t>
-  </si>
-  <si>
-    <t>91.1% (84.4%-94.9%)</t>
-  </si>
-  <si>
-    <t>90.3% (83.7%-94.4%)</t>
-  </si>
-  <si>
-    <t>91.1% (84.7%-94.9%)</t>
-  </si>
-  <si>
-    <t>91.7% (85.6%-95.2%)</t>
-  </si>
-  <si>
-    <t>92.1% (86.5%-95.5%)</t>
-  </si>
-  <si>
-    <t>93.9% (89.1%-96.7%)</t>
-  </si>
-  <si>
-    <t>95.2% (91.2%-97.6%)</t>
-  </si>
-  <si>
-    <t>92.3% (86.7%-95.6%)</t>
-  </si>
-  <si>
-    <t>94.2% (89.9%-97.0%)</t>
-  </si>
-  <si>
-    <t>95.5% (91.8%-97.8%)</t>
-  </si>
-  <si>
-    <t>86.9% (77.2%-92.7%)</t>
-  </si>
-  <si>
-    <t>325 (141-697)</t>
-  </si>
-  <si>
-    <t>298 (125-671)</t>
-  </si>
-  <si>
-    <t>280 (116-652)</t>
-  </si>
-  <si>
-    <t>267 (106-632)</t>
-  </si>
-  <si>
-    <t>279 (117-610)</t>
-  </si>
-  <si>
-    <t>242 (100-536)</t>
-  </si>
-  <si>
-    <t>210 (85.6-461)</t>
-  </si>
-  <si>
-    <t>298 (125-670)</t>
-  </si>
-  <si>
-    <t>280 (115-650)</t>
-  </si>
-  <si>
-    <t>266 (106-628)</t>
-  </si>
-  <si>
-    <t>209 (85.5-461)</t>
-  </si>
-  <si>
-    <t>624 (246-1,189)</t>
-  </si>
-  <si>
-    <t>566 (219-1,384)</t>
-  </si>
-  <si>
-    <t>530 (205-1,332)</t>
-  </si>
-  <si>
-    <t>511 (195-1,311)</t>
-  </si>
-  <si>
-    <t>493 (186-1,299)</t>
-  </si>
-  <si>
-    <t>464 (179-1,131)</t>
-  </si>
-  <si>
-    <t>375 (143-899)</t>
-  </si>
-  <si>
-    <t>290 (113-677)</t>
-  </si>
-  <si>
-    <t>521 (201-1,306)</t>
-  </si>
-  <si>
-    <t>494 (190-1,256)</t>
-  </si>
-  <si>
-    <t>471 (179-1,220)</t>
-  </si>
-  <si>
-    <t>458 (177-1,097)</t>
-  </si>
-  <si>
-    <t>365 (141-863)</t>
-  </si>
-  <si>
-    <t>280 (110-638)</t>
-  </si>
-  <si>
-    <t>906 (364-1,689)</t>
+    <t>103,412 (90,663-117,419)</t>
+  </si>
+  <si>
+    <t>103,322 (90,560-117,171)</t>
+  </si>
+  <si>
+    <t>103,187 (90,438-116,973)</t>
+  </si>
+  <si>
+    <t>103,079 (90,327-116,812)</t>
+  </si>
+  <si>
+    <t>103,322 (90,559-117,170)</t>
+  </si>
+  <si>
+    <t>103,187 (90,439-116,971)</t>
+  </si>
+  <si>
+    <t>103,077 (90,328-116,809)</t>
+  </si>
+  <si>
+    <t>103,237 (90,471-117,099)</t>
+  </si>
+  <si>
+    <t>103,012 (90,261-116,836)</t>
+  </si>
+  <si>
+    <t>102,858 (90,073-116,615)</t>
+  </si>
+  <si>
+    <t>103,237 (90,471-117,098)</t>
+  </si>
+  <si>
+    <t>103,012 (90,262-116,834)</t>
+  </si>
+  <si>
+    <t>102,856 (90,075-116,612)</t>
+  </si>
+  <si>
+    <t>103,830 (90,581-118,007)</t>
+  </si>
+  <si>
+    <t>141,264 (112,613-183,500)</t>
+  </si>
+  <si>
+    <t>140,485 (111,871-182,870)</t>
+  </si>
+  <si>
+    <t>140,020 (111,304-181,676)</t>
+  </si>
+  <si>
+    <t>139,672 (110,856-180,931)</t>
+  </si>
+  <si>
+    <t>140,457 (111,795-182,903)</t>
+  </si>
+  <si>
+    <t>139,999 (111,145-181,295)</t>
+  </si>
+  <si>
+    <t>139,580 (110,611-180,684)</t>
+  </si>
+  <si>
+    <t>139,632 (110,969-181,146)</t>
+  </si>
+  <si>
+    <t>138,374 (109,695-178,853)</t>
+  </si>
+  <si>
+    <t>137,373 (108,676-177,453)</t>
+  </si>
+  <si>
+    <t>139,629 (110,903-181,004)</t>
+  </si>
+  <si>
+    <t>138,307 (109,569-178,763)</t>
+  </si>
+  <si>
+    <t>137,311 (108,501-177,319)</t>
+  </si>
+  <si>
+    <t>143,485 (114,879-185,731)</t>
+  </si>
+  <si>
+    <t>10,721 (7,570-15,564)</t>
+  </si>
+  <si>
+    <t>10,649 (7,525-15,466)</t>
+  </si>
+  <si>
+    <t>10,585 (7,470-15,373)</t>
+  </si>
+  <si>
+    <t>10,561 (7,415-15,324)</t>
+  </si>
+  <si>
+    <t>10,585 (7,468-15,364)</t>
+  </si>
+  <si>
+    <t>10,560 (7,411-15,315)</t>
+  </si>
+  <si>
+    <t>10,579 (7,459-15,392)</t>
+  </si>
+  <si>
+    <t>10,459 (7,317-15,246)</t>
+  </si>
+  <si>
+    <t>10,333 (7,237-15,122)</t>
+  </si>
+  <si>
+    <t>10,577 (7,459-15,392)</t>
+  </si>
+  <si>
+    <t>10,457 (7,317-15,242)</t>
+  </si>
+  <si>
+    <t>10,330 (7,236-15,120)</t>
+  </si>
+  <si>
+    <t>11,008 (7,823-15,733)</t>
+  </si>
+  <si>
+    <t>14,073 (8,658-24,505)</t>
+  </si>
+  <si>
+    <t>13,859 (8,519-24,313)</t>
+  </si>
+  <si>
+    <t>13,734 (8,475-24,166)</t>
+  </si>
+  <si>
+    <t>13,629 (8,400-24,048)</t>
+  </si>
+  <si>
+    <t>13,844 (8,518-24,300)</t>
+  </si>
+  <si>
+    <t>13,686 (8,420-24,131)</t>
+  </si>
+  <si>
+    <t>13,565 (8,322-23,926)</t>
+  </si>
+  <si>
+    <t>13,558 (8,264-23,902)</t>
+  </si>
+  <si>
+    <t>13,196 (8,054-23,366)</t>
+  </si>
+  <si>
+    <t>12,945 (7,849-22,974)</t>
+  </si>
+  <si>
+    <t>13,539 (8,251-23,892)</t>
+  </si>
+  <si>
+    <t>13,162 (8,030-23,336)</t>
+  </si>
+  <si>
+    <t>12,873 (7,820-22,933)</t>
+  </si>
+  <si>
+    <t>14,721 (9,212-25,511)</t>
+  </si>
+  <si>
+    <t>2,135 (998-4,077)</t>
+  </si>
+  <si>
+    <t>2,110 (983-4,038)</t>
+  </si>
+  <si>
+    <t>2,088 (970-4,007)</t>
+  </si>
+  <si>
+    <t>2,073 (960-3,982)</t>
+  </si>
+  <si>
+    <t>2,109 (982-4,034)</t>
+  </si>
+  <si>
+    <t>2,088 (970-3,998)</t>
+  </si>
+  <si>
+    <t>2,071 (959-3,967)</t>
+  </si>
+  <si>
+    <t>2,017 (929-3,921)</t>
+  </si>
+  <si>
+    <t>1,910 (871-3,745)</t>
+  </si>
+  <si>
+    <t>1,819 (826-3,644)</t>
+  </si>
+  <si>
+    <t>1,906 (870-3,741)</t>
+  </si>
+  <si>
+    <t>1,817 (825-3,643)</t>
+  </si>
+  <si>
+    <t>2,346 (1,112-4,537)</t>
+  </si>
+  <si>
+    <t>2,998 (1,249-7,067)</t>
+  </si>
+  <si>
+    <t>2,922 (1,214-6,977)</t>
+  </si>
+  <si>
+    <t>2,874 (1,180-6,887)</t>
+  </si>
+  <si>
+    <t>2,830 (1,154-6,835)</t>
+  </si>
+  <si>
+    <t>2,911 (1,211-6,949)</t>
+  </si>
+  <si>
+    <t>2,836 (1,172-6,784)</t>
+  </si>
+  <si>
+    <t>2,769 (1,141-6,597)</t>
+  </si>
+  <si>
+    <t>2,621 (1,038-6,434)</t>
+  </si>
+  <si>
+    <t>2,344 (872-5,946)</t>
+  </si>
+  <si>
+    <t>2,132 (768-5,609)</t>
+  </si>
+  <si>
+    <t>2,609 (1,033-6,369)</t>
+  </si>
+  <si>
+    <t>2,311 (868-5,851)</t>
+  </si>
+  <si>
+    <t>2,084 (761-5,490)</t>
+  </si>
+  <si>
+    <t>3,668 (1,592-8,179)</t>
+  </si>
+  <si>
+    <t>88.4% (83.0%-92.6%)</t>
+  </si>
+  <si>
+    <t>89.0% (83.8%-93.1%)</t>
+  </si>
+  <si>
+    <t>89.4% (84.3%-93.5%)</t>
+  </si>
+  <si>
+    <t>89.8% (84.7%-93.8%)</t>
+  </si>
+  <si>
+    <t>89.4% (84.4%-93.5%)</t>
+  </si>
+  <si>
+    <t>89.8% (84.8%-93.9%)</t>
+  </si>
+  <si>
+    <t>90.0% (85.0%-93.8%)</t>
+  </si>
+  <si>
+    <t>91.3% (86.6%-94.8%)</t>
+  </si>
+  <si>
+    <t>92.3% (87.9%-95.5%)</t>
+  </si>
+  <si>
+    <t>86.1% (78.5%-91.9%)</t>
+  </si>
+  <si>
+    <t>90.2% (84.9%-94.2%)</t>
+  </si>
+  <si>
+    <t>90.9% (85.9%-94.7%)</t>
+  </si>
+  <si>
+    <t>91.5% (86.8%-95.0%)</t>
+  </si>
+  <si>
+    <t>91.9% (87.4%-95.3%)</t>
+  </si>
+  <si>
+    <t>91.1% (86.1%-94.7%)</t>
+  </si>
+  <si>
+    <t>91.8% (87.1%-95.2%)</t>
+  </si>
+  <si>
+    <t>92.4% (88.1%-95.5%)</t>
+  </si>
+  <si>
+    <t>92.7% (88.1%-96.0%)</t>
+  </si>
+  <si>
+    <t>94.4% (90.6%-97.0%)</t>
+  </si>
+  <si>
+    <t>95.6% (92.2%-97.7%)</t>
+  </si>
+  <si>
+    <t>92.8% (88.3%-96.0%)</t>
+  </si>
+  <si>
+    <t>94.6% (90.9%-97.1%)</t>
+  </si>
+  <si>
+    <t>95.9% (92.6%-97.9%)</t>
+  </si>
+  <si>
+    <t>86.6% (78.0%-92.7%)</t>
+  </si>
+  <si>
+    <t>300 (133-591)</t>
+  </si>
+  <si>
+    <t>271 (122-547)</t>
+  </si>
+  <si>
+    <t>251 (111-515)</t>
+  </si>
+  <si>
+    <t>234 (103-491)</t>
+  </si>
+  <si>
+    <t>257 (114-519)</t>
+  </si>
+  <si>
+    <t>220 (97.5-455)</t>
+  </si>
+  <si>
+    <t>190 (83.6-393)</t>
+  </si>
+  <si>
+    <t>271 (121-547)</t>
+  </si>
+  <si>
+    <t>251 (111-514)</t>
+  </si>
+  <si>
+    <t>234 (103-490)</t>
+  </si>
+  <si>
+    <t>220 (97.5-454)</t>
+  </si>
+  <si>
+    <t>190 (83.5-392)</t>
+  </si>
+  <si>
+    <t>707 (275-1,346)</t>
+  </si>
+  <si>
+    <t>514 (221-1,029)</t>
+  </si>
+  <si>
+    <t>475 (204-966)</t>
+  </si>
+  <si>
+    <t>446 (192-931)</t>
+  </si>
+  <si>
+    <t>428 (184-894)</t>
+  </si>
+  <si>
+    <t>422 (181-849)</t>
+  </si>
+  <si>
+    <t>341 (146-694)</t>
+  </si>
+  <si>
+    <t>268 (114-557)</t>
+  </si>
+  <si>
+    <t>470 (202-951)</t>
+  </si>
+  <si>
+    <t>436 (188-906)</t>
+  </si>
+  <si>
+    <t>414 (176-866)</t>
+  </si>
+  <si>
+    <t>416 (179-841)</t>
+  </si>
+  <si>
+    <t>335 (143-684)</t>
+  </si>
+  <si>
+    <t>263 (112-544)</t>
+  </si>
+  <si>
+    <t>992 (397-1,794)</t>
   </si>
 </sst>
 </file>
@@ -849,25 +846,25 @@
         <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -881,25 +878,25 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -913,25 +910,25 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -945,25 +942,25 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -974,28 +971,28 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1006,28 +1003,28 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
         <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1038,28 +1035,28 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1070,28 +1067,28 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1102,28 +1099,28 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1134,28 +1131,28 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1166,28 +1163,28 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1198,28 +1195,28 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1230,28 +1227,28 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1262,28 +1259,28 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
